--- a/data/trans_orig/IP16A08-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A08-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24806</t>
+          <t>25752</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>22263</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28315</t>
+          <t>28345</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50099</t>
+          <t>49708</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57144</t>
+          <t>57030</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>12419</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19433</t>
+          <t>18735</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31197</t>
+          <t>30802</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39879</t>
+          <t>39630</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40683</t>
+          <t>40763</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48159</t>
+          <t>48310</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74748</t>
+          <t>75446</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86602</t>
+          <t>86625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,98%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>9884</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>9018</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16146</t>
+          <t>16191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>12623</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19872</t>
+          <t>19809</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>14848</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21534</t>
+          <t>21415</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30227</t>
+          <t>30182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39596</t>
+          <t>39746</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10139</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>22283</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20385</t>
+          <t>19899</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27166</t>
+          <t>27481</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25602</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34011</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48625</t>
+          <t>47698</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59842</t>
+          <t>59477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>84,99%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26859</t>
+          <t>26910</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31549</t>
+          <t>31017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34147</t>
+          <t>32995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53489</t>
+          <t>52511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98446</t>
+          <t>98395</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111893</t>
+          <t>112347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112370</t>
+          <t>112902</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126882</t>
+          <t>127243</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>215735</t>
+          <t>216713</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235077</t>
+          <t>236229</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,74%</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31760</t>
+          <t>32631</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34838</t>
+          <t>35778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68584</t>
+          <t>70342</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74356</t>
+          <t>74358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16872</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44110</t>
+          <t>43778</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51682</t>
+          <t>51521</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56911</t>
+          <t>56758</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64165</t>
+          <t>64125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103570</t>
+          <t>104375</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>114678</t>
+          <t>114523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9609</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>12766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8809</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19525</t>
+          <t>19574</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20261</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27311</t>
+          <t>27353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15460</t>
+          <t>15149</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23436</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38260</t>
+          <t>38211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48976</t>
+          <t>49315</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>10807</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7627</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>17982</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>16362</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23815</t>
+          <t>23865</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>14964</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21901</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33973</t>
+          <t>34055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44410</t>
+          <t>44715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11969</t>
+          <t>12225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>25543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13322</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27433</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>28961</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47421</t>
+          <t>47480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121864</t>
+          <t>121678</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135252</t>
+          <t>134996</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130533</t>
+          <t>129372</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>144644</t>
+          <t>143842</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>257766</t>
+          <t>257707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>276651</t>
+          <t>276226</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23297</t>
+          <t>23238</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18548</t>
+          <t>18138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23329</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44343</t>
+          <t>44015</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49753</t>
+          <t>49814</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>555</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13144</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36039</t>
+          <t>35211</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41687</t>
+          <t>41684</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33059</t>
+          <t>33320</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40711</t>
+          <t>40936</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>72191</t>
+          <t>72132</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81526</t>
+          <t>81174</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>13412</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>11286</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21548</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>22712</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31020</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>22160</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30536</t>
+          <t>30412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48022</t>
+          <t>47972</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59569</t>
+          <t>59458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8781</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15221</t>
+          <t>15420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19758</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13977</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29602</t>
+          <t>29403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39407</t>
+          <t>39023</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,06%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25387</t>
+          <t>24797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25702</t>
+          <t>25464</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27028</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45709</t>
+          <t>45555</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102074</t>
+          <t>102664</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115485</t>
+          <t>115646</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97574</t>
+          <t>97812</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111374</t>
+          <t>111171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>205028</t>
+          <t>205182</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>223709</t>
+          <t>223401</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,1%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>12514</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38804</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45428</t>
+          <t>45334</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37667</t>
+          <t>36470</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46458</t>
+          <t>45912</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79142</t>
+          <t>79512</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>10056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16805</t>
+          <t>17039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>27132</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34102</t>
+          <t>34748</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36192</t>
+          <t>36113</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44083</t>
+          <t>44221</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66515</t>
+          <t>66281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77702</t>
+          <t>77071</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13350</t>
+          <t>12613</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13487</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20946</t>
+          <t>21811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64607</t>
+          <t>65344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76417</t>
+          <t>76505</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51205</t>
+          <t>51474</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61053</t>
+          <t>61254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>121703</t>
+          <t>120838</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136264</t>
+          <t>136142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27454</t>
+          <t>27497</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>23828</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45449</t>
+          <t>45074</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154592</t>
+          <t>155193</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169939</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154747</t>
+          <t>154704</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170348</t>
+          <t>170310</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>314467</t>
+          <t>314842</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>337250</t>
+          <t>336088</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A08-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A08-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3642</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7283</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>711</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3283</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4185</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3642</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7392</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26013</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22372</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28216</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,72%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,15%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>28324</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>25752</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24850</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,55%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>85,59%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>26013</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>22263</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28345</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>87,72%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>75,07%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>84</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49708</t>
+          <t>50150</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57030</t>
+          <t>57028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5605</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9871</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,37%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6734</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3591</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12419</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3565</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11553</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>15,58%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28,73%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5605</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2650</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10197</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>19279</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>45355</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>41089</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>48221</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,63%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,62%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>30802</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39630</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>31668</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>39656</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>84,42%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>45355</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>40763</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>48310</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75446</t>
+          <t>74902</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86625</t>
+          <t>86321</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1414,67 +1414,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>5166</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2570</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8833</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,65%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>37,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>5642</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2698</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9884</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2854</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9500</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>25,07%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5166</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2451</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9018</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,65%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16191</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18700</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15033</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21296</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>78,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>62,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,23%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>16865</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12623</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19809</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13007</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>19653</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>74,93%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>56,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,01%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>18700</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>14848</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>21415</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>78,35%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30182</t>
+          <t>30651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39746</t>
+          <t>39775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8998</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5595</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13990</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>35,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6279</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3062</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10644</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3229</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10927</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>20,56%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>34,85%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8998</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5266</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>14489</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>22,82%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22283</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30440</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25448</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>33843</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>77,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>64,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>24264</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19899</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>27481</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19616</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>27314</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>79,44%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>65,15%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>30440</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>24949</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>34172</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>77,18%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47698</t>
+          <t>48785</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59477</t>
+          <t>59473</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,98%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23411</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16713</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30782</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>16,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,61%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>19366</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12958</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>26910</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>13711</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>27978</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>15,45%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>23411</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>16676</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>31017</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>16,27%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32995</t>
+          <t>34029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52511</t>
+          <t>53746</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>120508</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>113137</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>127206</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>83,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>78,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>88,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>105939</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>98395</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>112347</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>97327</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>111594</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>84,55%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>78,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>120508</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>112902</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>127243</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>83,73%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216713</t>
+          <t>215478</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>236229</t>
+          <t>235195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,36%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3319</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1246</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3866</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4350</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,41%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2648</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -2788,69 +2788,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>37798</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35107</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>35251</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>32631</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>32147</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>36497</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,59%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,41%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>88,08%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>37798</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>35778</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>93,11%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>106</t>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70342</t>
+          <t>69867</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74358</t>
+          <t>74360</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>36497</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>36497</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>36497</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5451</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10130</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15,17%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4783</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2164</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9907</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2151</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9890</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,91%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5451</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2632</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9999</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16067</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>61306</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>56627</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>64102</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,84%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>48902</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>43778</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>51521</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>43795</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>51534</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,09%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,97%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>61306</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>56758</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>64125</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,84%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104375</t>
+          <t>104077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>114523</t>
+          <t>114496</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>66757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>66757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>66757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>53685</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>53685</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>53685</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>66757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>66757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>66757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,107 +3356,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7942</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4430</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12443</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>28,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,87%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>44,57%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5536</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2517</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9645</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2276</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>18,53%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7942</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4216</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12766</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>28,45%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>33,82%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>13477</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>8728</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>19749</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>23,32%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>15,1%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>45,73%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>13477</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>8470</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>19574</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>23,32%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -3469,107 +3469,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>19973</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15472</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23485</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>71,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>55,43%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,13%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>24334</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20225</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27353</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>19769</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>27594</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>81,47%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>67,71%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,57%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>19973</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>15149</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>23699</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>71,55%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>44308</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>38036</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>49057</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>76,68%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>65,82%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>84,9%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>44308</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>38211</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>49315</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>76,68%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>66,13%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>29870</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>29870</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>29870</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6024</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2851</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10345</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,22%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>41,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6193</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3304</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10807</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3273</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9926</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>22,79%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>39,78%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6024</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2824</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18844</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14523</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22017</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>75,78%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>58,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>20976</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16362</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23865</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>17243</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>23896</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>77,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>18844</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>14964</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>22044</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>75,78%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34055</t>
+          <t>34321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44715</t>
+          <t>44584</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,68%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>27169</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>27169</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>27169</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13676</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>27640</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>17,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>17758</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12225</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25543</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>11906</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>25693</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>12,06%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,35%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20044</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>14124</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>28594</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28961</t>
+          <t>28283</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47480</t>
+          <t>49257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>137922</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>130326</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>144290</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,31%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>82,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>91,34%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>129463</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>121678</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>134996</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>121528</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>135315</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>87,94%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>82,65%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,7%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>137922</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>129372</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>143842</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,31%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>257707</t>
+          <t>255930</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>276226</t>
+          <t>276904</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>147221</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1174</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3795</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3994</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,34%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5838</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21978</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18717</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23341</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,06%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>25859</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23238</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>23039</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,66%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,96%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>85,23%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21978</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>18138</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23332</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>75,65%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>77</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44015</t>
+          <t>44240</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49814</t>
+          <t>49742</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5329</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2323</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10352</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2406</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7028</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6450</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,7%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5329</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2160</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9776</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37767</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32744</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40773</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,64%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>75,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>39833</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>35211</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>41684</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>35789</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>41678</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>37767</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>33320</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>40936</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>87,64%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>72132</t>
+          <t>71929</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81174</t>
+          <t>81069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,107 +5303,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6348</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3429</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10441</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,25%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8734</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4985</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13412</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4981</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13516</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>24,18%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>37,42%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>15082</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>9598</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>21358</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>21,68%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>13,8%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6348</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3034</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11286</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>18,98%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>33,74%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>15082</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>10112</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>21598</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>21,68%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -5416,107 +5416,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27098</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23005</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30017</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>81,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>68,78%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,75%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>27390</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22712</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>31139</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>22608</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>31143</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>75,82%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>62,58%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>86,21%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>54488</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>48212</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>59972</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>78,32%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>69,3%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>86,2%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>27098</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>22160</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>30412</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>81,02%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>66,26%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>90,93%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>54488</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>47972</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>59458</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>78,32%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>68,96%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4600</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2140</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,21%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5310</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2668</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9490</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9032</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>24,06%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>43,01%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4600</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8280</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>20,21%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18158</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14459</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20618</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>79,79%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>16755</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12575</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19397</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>13033</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>19881</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>75,94%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>56,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>18158</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>14478</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>20660</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>79,79%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29403</t>
+          <t>29944</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39023</t>
+          <t>39361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -5877,52 +5877,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>22065</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18275</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12814</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25905</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,39%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,01%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>17623</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11815</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24797</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>12002</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>25156</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>13,83%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>18275</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>12105</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>25464</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27336</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45555</t>
+          <t>49384</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>105001</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>97371</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>110462</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>85,18%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>78,99%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,61%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>109838</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>102664</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>115646</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>102305</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>115459</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>86,17%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>80,55%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>90,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>105001</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>97812</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>111171</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>85,18%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>205182</t>
+          <t>201353</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>223401</t>
+          <t>223081</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>14169</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22357</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>72</t>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4582</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8558</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,75%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3584</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1289</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7778</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,69%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12514</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9773</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16095</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>43039</t>
+          <t>36653</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>32677</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45334</t>
+          <t>39140</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>42795</t>
+          <t>37273</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36470</t>
+          <t>33168</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45912</t>
+          <t>39497</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>85834</t>
+          <t>73926</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79512</t>
+          <t>68674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90334</t>
+          <t>77489</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4809</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10153</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,94%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5577</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2403</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10019</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>10920</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10578</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17039</t>
+          <t>17509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39162</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>33818</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>41987</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,06%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>31574</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>27132</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>34748</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>84,99%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>73,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41167</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36113</t>
+          <t>27028</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44221</t>
+          <t>35366</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>72742</t>
+          <t>71292</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66281</t>
+          <t>64410</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77071</t>
+          <t>75892</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7691</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3766</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13883</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5826</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1452</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12613</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,47%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>11460</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>13742</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21811</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>54622</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>48430</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>58547</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,96%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>72131</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>65344</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>76505</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,53%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>57273</t>
+          <t>43929</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51474</t>
+          <t>38520</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61254</t>
+          <t>47185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>129405</t>
+          <t>98551</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>120838</t>
+          <t>91425</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136142</t>
+          <t>104366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17083</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11064</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25466</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>14986</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7779</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>22522</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11891</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27497</t>
+          <t>23447</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>32574</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23828</t>
+          <t>23936</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45074</t>
+          <t>42490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>147869</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>139486</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>153888</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>162729</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>155193</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>169936</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>91,57%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,33%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>163592</t>
+          <t>127500</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154704</t>
+          <t>119545</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170310</t>
+          <t>133259</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>326321</t>
+          <t>275370</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>314842</t>
+          <t>265454</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>336088</t>
+          <t>284008</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
